--- a/Luban/Config/Datas/#TimeConfig.xlsx
+++ b/Luban/Config/Datas/#TimeConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AF9932-A9BE-4812-BE43-E0A7ECC1D0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8378C47-4950-4268-AD6A-E48B127AD39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="8850" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="9150" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
